--- a/textbook_examples/mod01_sorting_filtering.xlsx
+++ b/textbook_examples/mod01_sorting_filtering.xlsx
@@ -1,127 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usaskca1-my.sharepoint.com/personal/pjs998_usask_ca/Documents/Teaching/261/2026/textbook_261/textbook_examples/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{F03F9AC9-CA95-EE40-8EC5-B70067A72F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{722884BD-65C5-674F-A145-F5853D417057}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{EC933C14-BD57-7348-97DE-4449601A7759}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Complete" sheetId="1" r:id="rId1"/>
-    <sheet name="Practice" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Complete" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Complete!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Complete'!$A$1:$D$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="15">
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Crop</t>
-  </si>
-  <si>
-    <t>Acres</t>
-  </si>
-  <si>
-    <t>Yield (bu/ac)</t>
-  </si>
-  <si>
-    <t>North</t>
-  </si>
-  <si>
-    <t>Canola</t>
-  </si>
-  <si>
-    <t>South</t>
-  </si>
-  <si>
-    <t>Wheat</t>
-  </si>
-  <si>
-    <t>Creek</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Barley</t>
-  </si>
-  <si>
-    <t>Rented</t>
-  </si>
-  <si>
-    <t>Airport</t>
-  </si>
-  <si>
-    <t>Hill</t>
-  </si>
-  <si>
-    <t>Slough</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF24302A"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF24302A"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -145,37 +69,96 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -495,305 +478,365 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57013188-87E9-DC4C-B229-2244E7096734}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="4" width="17.83203125" customWidth="1"/>
+    <col width="17.83203125" customWidth="1" min="1" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="5">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Crop</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Acres</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Yield (bu/ac)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>320</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="6" t="n">
         <v>41.2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="5">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="6" t="n">
         <v>58.6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="5">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Creek</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="6" t="n">
         <v>37.9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Barley</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>210</v>
       </c>
-      <c r="D5" s="6">
-        <v>72.400000000000006</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="D5" s="6" t="n">
+        <v>72.40000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Rented</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="6" t="n">
         <v>61.3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="5">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Airport</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="6" t="n">
         <v>44.8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="5">
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Barley</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>275</v>
       </c>
-      <c r="D8" s="6">
-        <v>68.099999999999994</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="D8" s="6" t="n">
+        <v>68.09999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Slough</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
         <v>330</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="6" t="n">
         <v>55.2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="5">
-        <v>400</v>
-      </c>
-      <c r="D10" s="6">
-        <v>61.3</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{57013188-87E9-DC4C-B229-2244E7096734}"/>
+  <autoFilter ref="A1:D1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{169CCBDE-6E34-2A4C-BE9D-E9FA51E030DA}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="4" width="17.83203125" customWidth="1"/>
+    <col width="17.83203125" customWidth="1" min="1" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="5">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Crop</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Acres</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Yield (bu/ac)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>320</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="6" t="n">
         <v>41.2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="5">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="6" t="n">
         <v>58.6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="5">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Creek</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="6" t="n">
         <v>37.9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Barley</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>210</v>
       </c>
-      <c r="D5" s="6">
-        <v>72.400000000000006</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="D5" s="6" t="n">
+        <v>72.40000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Rented</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="6" t="n">
         <v>61.3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="5">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Airport</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="6" t="n">
         <v>44.8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="5">
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Barley</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>275</v>
       </c>
-      <c r="D8" s="6">
-        <v>68.099999999999994</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="D8" s="6" t="n">
+        <v>68.09999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Slough</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
         <v>330</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="6" t="n">
         <v>55.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="5">
-        <v>400</v>
-      </c>
-      <c r="D10" s="6">
-        <v>61.3</v>
       </c>
     </row>
   </sheetData>
